--- a/kanban_system/output/library_linked/新加坡法规清单.xlsx
+++ b/kanban_system/output/library_linked/新加坡法规清单.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新加坡" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="车辆安全标准涉及项目" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="车辆附加技术需求" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="新加坡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="车辆安全标准涉及项目" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="车辆附加技术需求" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="152511" fullCalcOnLoad="1"/>
@@ -6467,7 +6467,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>除了新加坡的一般车辆安全标准外，每种类型的车辆还有额外的技术要求。附加技术需求矩阵如下：</t>
         </is>
